--- a/sonha_vat_tu/static/xls/bom_templates.xlsx
+++ b/sonha_vat_tu/static/xls/bom_templates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\odoo17\sonha\odoo-customize\sonha_vat_tu\static\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CC90B3-B916-4211-AF25-D9EDDCDC2724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD482FFF-62E9-4E4C-8696-A82A92F9AB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{14BF3EAE-7F97-4B53-87F7-5FB33363E879}"/>
   </bookViews>
@@ -97,6 +97,7 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -110,7 +111,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FF3F6F8F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -158,6 +159,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF3F6F8F"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
